--- a/data/samples/atlas_erp_migration.xlsx
+++ b/data/samples/atlas_erp_migration.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,21 @@
           <t>Actual Finish date</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Effort (hours)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Effort completed (hours)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Effort remaining (hours)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,7 +554,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -567,7 +582,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -589,6 +604,15 @@
         <is>
           <t>2026-02-10</t>
         </is>
+      </c>
+      <c r="T2" t="n">
+        <v>84</v>
+      </c>
+      <c r="U2" t="n">
+        <v>84</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -609,7 +633,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -642,7 +666,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -654,6 +678,15 @@
         <is>
           <t>2026-02-16</t>
         </is>
+      </c>
+      <c r="T3" t="n">
+        <v>16</v>
+      </c>
+      <c r="U3" t="n">
+        <v>16</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -679,12 +712,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -697,7 +730,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -717,7 +750,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -729,6 +762,15 @@
         <is>
           <t>2026-02-21</t>
         </is>
+      </c>
+      <c r="T4" t="n">
+        <v>80</v>
+      </c>
+      <c r="U4" t="n">
+        <v>80</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -754,12 +796,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>T. Bauer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -772,7 +814,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -792,7 +834,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -804,6 +846,15 @@
         <is>
           <t>2026-02-27</t>
         </is>
+      </c>
+      <c r="T5" t="n">
+        <v>24</v>
+      </c>
+      <c r="U5" t="n">
+        <v>24</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -819,12 +870,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>N. Kaur</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -847,7 +898,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -857,7 +908,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -869,6 +920,15 @@
         <is>
           <t>2026-03-04</t>
         </is>
+      </c>
+      <c r="T6" t="n">
+        <v>60</v>
+      </c>
+      <c r="U6" t="n">
+        <v>60</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -902,12 +962,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J. Park</t>
+          <t>V. Rao</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -930,7 +990,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -952,6 +1012,15 @@
         <is>
           <t>2026-03-10</t>
         </is>
+      </c>
+      <c r="T7" t="n">
+        <v>24</v>
+      </c>
+      <c r="U7" t="n">
+        <v>24</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -982,7 +1051,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -995,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1015,7 +1084,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1027,6 +1096,15 @@
         <is>
           <t>2026-03-15</t>
         </is>
+      </c>
+      <c r="T8" t="n">
+        <v>32</v>
+      </c>
+      <c r="U8" t="n">
+        <v>32</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1052,12 +1130,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1090,7 +1168,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1102,6 +1180,15 @@
         <is>
           <t>2026-03-21</t>
         </is>
+      </c>
+      <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>16</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1122,7 +1209,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1168,8 +1255,25 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="T10" t="n">
+        <v>24</v>
+      </c>
+      <c r="U10" t="n">
+        <v>24</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Approved Budget</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>150000</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -1182,7 +1286,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1210,7 +1314,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1220,7 +1324,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1232,6 +1336,15 @@
         <is>
           <t>2026-04-01</t>
         </is>
+      </c>
+      <c r="T11" t="n">
+        <v>33</v>
+      </c>
+      <c r="U11" t="n">
+        <v>33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1255,12 +1368,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>T. Bauer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1306,6 +1419,15 @@
           <t>2026-04-07</t>
         </is>
       </c>
+      <c r="T12" t="n">
+        <v>80</v>
+      </c>
+      <c r="U12" t="n">
+        <v>80</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="F13" t="inlineStr">
@@ -1320,7 +1442,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>N. Kaur</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1348,7 +1470,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1358,7 +1480,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1370,6 +1492,15 @@
         <is>
           <t>2026-04-12</t>
         </is>
+      </c>
+      <c r="T13" t="n">
+        <v>80</v>
+      </c>
+      <c r="U13" t="n">
+        <v>80</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1385,12 +1516,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>J. Park</t>
+          <t>V. Rao</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1413,7 +1544,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1423,7 +1554,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1435,6 +1566,15 @@
         <is>
           <t>2026-04-18</t>
         </is>
+      </c>
+      <c r="T14" t="n">
+        <v>16</v>
+      </c>
+      <c r="U14" t="n">
+        <v>16</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1455,7 +1595,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1488,7 +1628,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1500,6 +1640,15 @@
         <is>
           <t>2026-04-23</t>
         </is>
+      </c>
+      <c r="T15" t="n">
+        <v>32</v>
+      </c>
+      <c r="U15" t="n">
+        <v>32</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1515,7 +1664,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1553,7 +1702,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1565,6 +1714,15 @@
         <is>
           <t>2026-04-29</t>
         </is>
+      </c>
+      <c r="T16" t="n">
+        <v>33</v>
+      </c>
+      <c r="U16" t="n">
+        <v>33</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1585,7 +1743,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1598,7 +1756,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1630,6 +1788,15 @@
         <is>
           <t>2026-05-04</t>
         </is>
+      </c>
+      <c r="T17" t="n">
+        <v>60</v>
+      </c>
+      <c r="U17" t="n">
+        <v>60</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1645,7 +1812,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1683,7 +1850,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1695,6 +1862,15 @@
         <is>
           <t>2026-05-10</t>
         </is>
+      </c>
+      <c r="T18" t="n">
+        <v>24</v>
+      </c>
+      <c r="U18" t="n">
+        <v>24</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1718,12 +1894,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>T. Bauer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1736,7 +1912,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1756,7 +1932,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1768,6 +1944,15 @@
         <is>
           <t>2026-05-15</t>
         </is>
+      </c>
+      <c r="T19" t="n">
+        <v>24</v>
+      </c>
+      <c r="U19" t="n">
+        <v>24</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1783,7 +1968,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>N. Kaur</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1834,6 +2019,15 @@
           <t>2026-05-21</t>
         </is>
       </c>
+      <c r="T20" t="n">
+        <v>24</v>
+      </c>
+      <c r="U20" t="n">
+        <v>24</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="F21" t="inlineStr">
@@ -1848,12 +2042,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>J. Park</t>
+          <t>V. Rao</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1886,7 +2080,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1898,6 +2092,15 @@
         <is>
           <t>2026-05-26</t>
         </is>
+      </c>
+      <c r="T21" t="n">
+        <v>80</v>
+      </c>
+      <c r="U21" t="n">
+        <v>80</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1918,7 +2121,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1931,7 +2134,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1951,7 +2154,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -1963,6 +2166,15 @@
         <is>
           <t>2026-06-01</t>
         </is>
+      </c>
+      <c r="T22" t="n">
+        <v>16</v>
+      </c>
+      <c r="U22" t="n">
+        <v>16</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1978,12 +2190,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2016,7 +2228,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2028,6 +2240,15 @@
         <is>
           <t>2026-06-06</t>
         </is>
+      </c>
+      <c r="T23" t="n">
+        <v>60</v>
+      </c>
+      <c r="U23" t="n">
+        <v>60</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2056,7 +2277,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2089,7 +2310,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2101,6 +2322,15 @@
         <is>
           <t>2026-06-12</t>
         </is>
+      </c>
+      <c r="T24" t="n">
+        <v>60</v>
+      </c>
+      <c r="U24" t="n">
+        <v>60</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2116,7 +2346,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2134,7 +2364,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2154,7 +2384,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2166,6 +2396,15 @@
         <is>
           <t>2026-06-18</t>
         </is>
+      </c>
+      <c r="T25" t="n">
+        <v>80</v>
+      </c>
+      <c r="U25" t="n">
+        <v>80</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2181,12 +2420,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>T. Bauer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2195,11 +2434,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2226,6 +2465,15 @@
         <is>
           <t>2026-06-23</t>
         </is>
+      </c>
+      <c r="T26" t="n">
+        <v>60</v>
+      </c>
+      <c r="U26" t="n">
+        <v>30</v>
+      </c>
+      <c r="V26" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -2241,7 +2489,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>N. Kaur</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2259,7 +2507,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2269,7 +2517,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2281,6 +2529,15 @@
         <is>
           <t>2026-06-29</t>
         </is>
+      </c>
+      <c r="T27" t="n">
+        <v>24</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -2296,12 +2553,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>J. Park</t>
+          <t>V. Rao</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2336,6 +2593,15 @@
         <is>
           <t>2026-07-04</t>
         </is>
+      </c>
+      <c r="T28" t="n">
+        <v>24</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="29">
@@ -2356,7 +2622,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2391,6 +2657,15 @@
         <is>
           <t>2026-07-10</t>
         </is>
+      </c>
+      <c r="T29" t="n">
+        <v>56</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="30">
@@ -2406,12 +2681,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2446,6 +2721,15 @@
         <is>
           <t>2026-07-15</t>
         </is>
+      </c>
+      <c r="T30" t="n">
+        <v>22</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="31">
@@ -2474,7 +2758,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2487,7 +2771,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2497,7 +2781,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2509,6 +2793,15 @@
         <is>
           <t>2026-07-21</t>
         </is>
+      </c>
+      <c r="T31" t="n">
+        <v>16</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="32">
@@ -2524,12 +2817,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2564,6 +2857,15 @@
         <is>
           <t>2026-07-26</t>
         </is>
+      </c>
+      <c r="T32" t="n">
+        <v>32</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="33">
@@ -2579,12 +2881,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>T. Bauer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2619,6 +2921,15 @@
         <is>
           <t>2026-08-01</t>
         </is>
+      </c>
+      <c r="T33" t="n">
+        <v>33</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="34">
@@ -2634,12 +2945,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>N. Kaur</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2674,6 +2985,15 @@
         <is>
           <t>2026-08-06</t>
         </is>
+      </c>
+      <c r="T34" t="n">
+        <v>56</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="35">
@@ -2689,7 +3009,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>J. Park</t>
+          <t>V. Rao</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2717,7 +3037,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -2729,6 +3049,15 @@
         <is>
           <t>2026-08-12</t>
         </is>
+      </c>
+      <c r="T35" t="n">
+        <v>44</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -2757,7 +3086,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2792,6 +3121,15 @@
         <is>
           <t>2026-08-17</t>
         </is>
+      </c>
+      <c r="T36" t="n">
+        <v>44</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -2807,7 +3145,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2835,7 +3173,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -2847,6 +3185,15 @@
         <is>
           <t>2026-08-23</t>
         </is>
+      </c>
+      <c r="T37" t="n">
+        <v>16</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -2867,7 +3214,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2902,6 +3249,15 @@
         <is>
           <t>2026-08-29</t>
         </is>
+      </c>
+      <c r="T38" t="n">
+        <v>40</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -2917,12 +3273,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2935,7 +3291,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2957,6 +3313,15 @@
         <is>
           <t>2026-09-03</t>
         </is>
+      </c>
+      <c r="T39" t="n">
+        <v>32</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="40">
@@ -2972,12 +3337,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>T. Bauer</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2990,7 +3355,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3012,6 +3377,15 @@
         <is>
           <t>2026-09-09</t>
         </is>
+      </c>
+      <c r="T40" t="n">
+        <v>60</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
